--- a/data/trans_camb/LAWTONB_2R3-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/LAWTONB_2R3-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,17; 25,46</t>
+          <t>-8,14; 26,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,16; 21,76</t>
+          <t>-9,09; 23,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 27,09</t>
+          <t>-2,81; 28,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,69; 47,29</t>
+          <t>8,83; 46,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,29; 41,72</t>
+          <t>1,94; 40,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,79; 35,48</t>
+          <t>4,41; 35,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,68; 33,61</t>
+          <t>6,51; 31,93</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 27,43</t>
+          <t>2,94; 29,81</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,22; 28,65</t>
+          <t>5,95; 28,0</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-44,57; 349,41</t>
+          <t>-41,92; 335,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-45,47; 282,17</t>
+          <t>-46,14; 345,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-19,88; 401,48</t>
+          <t>-15,15; 474,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29,97; 614,35</t>
+          <t>25,41; 559,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,81; 511,79</t>
+          <t>0,24; 552,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,86; 515,19</t>
+          <t>10,42; 447,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,11; 341,94</t>
+          <t>22,71; 304,08</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 282,5</t>
+          <t>7,48; 290,72</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>28,38; 349,75</t>
+          <t>21,28; 291,0</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 22,75</t>
+          <t>-3,8; 23,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,78; 6,92</t>
+          <t>-12,93; 7,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,05; 11,24</t>
+          <t>-10,51; 10,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,81; 29,16</t>
+          <t>6,75; 29,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 23,27</t>
+          <t>0,85; 23,98</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,84; 27,04</t>
+          <t>8,82; 27,72</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,78; 22,72</t>
+          <t>5,96; 23,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 13,61</t>
+          <t>-2,05; 14,03</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,03; 18,83</t>
+          <t>4,18; 18,49</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-27,9; 414,73</t>
+          <t>-35,33; 394,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-72,82; 120,32</t>
+          <t>-70,17; 179,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-60,12; 250,01</t>
+          <t>-60,16; 207,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27,37; 335,39</t>
+          <t>33,68; 353,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 279,83</t>
+          <t>-3,4; 261,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,8; 317,31</t>
+          <t>40,99; 319,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,9; 259,83</t>
+          <t>33,44; 260,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-18,15; 158,63</t>
+          <t>-14,74; 159,14</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>27,94; 215,39</t>
+          <t>20,45; 204,85</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,26; 29,64</t>
+          <t>1,05; 28,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,87; 13,28</t>
+          <t>-8,01; 14,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,41; 24,74</t>
+          <t>2,44; 24,85</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,99; 16,85</t>
+          <t>-9,34; 16,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-20,79; 4,7</t>
+          <t>-21,73; 3,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 22,43</t>
+          <t>0,24; 23,58</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 18,68</t>
+          <t>-1,89; 19,09</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-11,98; 4,55</t>
+          <t>-12,99; 4,66</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,1; 21,34</t>
+          <t>4,49; 21,27</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 663,54</t>
+          <t>-5,64; 767,28</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-63,29; 309,94</t>
+          <t>-58,21; 375,66</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,2; 775,34</t>
+          <t>9,81; 611,39</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-36,55; 119,11</t>
+          <t>-36,36; 113,66</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-80,05; 43,61</t>
+          <t>-80,4; 38,61</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 163,25</t>
+          <t>-3,25; 172,88</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-8,53; 170,05</t>
+          <t>-10,74; 163,87</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-59,84; 41,26</t>
+          <t>-61,68; 43,43</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>15,57; 187,53</t>
+          <t>18,86; 203,83</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,32; 32,33</t>
+          <t>7,6; 32,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,62; 24,99</t>
+          <t>1,98; 23,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,36; 21,35</t>
+          <t>2,87; 21,65</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-10,37; 17,54</t>
+          <t>-10,63; 15,87</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-18,26; 10,69</t>
+          <t>-19,47; 10,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-12,92; 9,2</t>
+          <t>-12,56; 9,25</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,89; 20,22</t>
+          <t>-0,22; 19,68</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,9; 12,29</t>
+          <t>-5,31; 12,25</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 12,09</t>
+          <t>-3,76; 11,97</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>34,66; 1436,42</t>
+          <t>42,96; 1592,3</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 1230,66</t>
+          <t>2,02; 1113,27</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,1; 1112,82</t>
+          <t>6,11; 932,89</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-34,21; 106,25</t>
+          <t>-37,35; 94,74</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-60,6; 70,34</t>
+          <t>-59,28; 69,2</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-40,42; 61,27</t>
+          <t>-37,89; 55,49</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,82; 158,51</t>
+          <t>-1,04; 169,42</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-31,5; 115,12</t>
+          <t>-27,43; 104,15</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-16,95; 112,58</t>
+          <t>-15,73; 104,84</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-25,44; 16,31</t>
+          <t>-25,77; 16,13</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-35,63; -1,37</t>
+          <t>-35,94; -1,49</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-22,34; 12,14</t>
+          <t>-24,27; 10,76</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-21,36; 19,63</t>
+          <t>-20,94; 17,33</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-15,06; 24,91</t>
+          <t>-13,22; 26,02</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-22,82; 8,38</t>
+          <t>-23,22; 8,35</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-17,63; 11,57</t>
+          <t>-17,9; 11,08</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-19,87; 9,03</t>
+          <t>-18,2; 10,22</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-17,61; 5,58</t>
+          <t>-17,93; 6,0</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-72,03; 103,49</t>
+          <t>-72,93; 110,12</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-89,29; 10,29</t>
+          <t>-91,71; 6,92</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-62,03; 88,07</t>
+          <t>-63,75; 83,34</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-51,0; 103,29</t>
+          <t>-52,73; 91,88</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-38,51; 130,97</t>
+          <t>-33,52; 131,63</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-54,22; 44,33</t>
+          <t>-52,88; 45,3</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-48,57; 56,52</t>
+          <t>-49,22; 54,99</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-51,56; 49,6</t>
+          <t>-51,1; 49,5</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-46,9; 30,3</t>
+          <t>-46,5; 29,7</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 26,99</t>
+          <t>-5,09; 29,1</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-8,86; 22,4</t>
+          <t>-9,27; 21,62</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 25,83</t>
+          <t>0,26; 26,32</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 23,97</t>
+          <t>-4,33; 24,46</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 27,31</t>
+          <t>-2,5; 28,72</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,82; 32,46</t>
+          <t>7,42; 31,62</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,34; 22,56</t>
+          <t>0,14; 21,29</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 21,63</t>
+          <t>-0,85; 21,59</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>7,46; 25,42</t>
+          <t>7,87; 25,26</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-25,68; 272,25</t>
+          <t>-25,4; 266,81</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-37,21; 236,28</t>
+          <t>-38,98; 206,78</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 263,26</t>
+          <t>-1,12; 295,06</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-23,47; 227,06</t>
+          <t>-21,91; 230,41</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-16,92; 261,53</t>
+          <t>-16,65; 278,97</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>37,01; 380,03</t>
+          <t>28,38; 371,27</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 183,1</t>
+          <t>0,21; 186,33</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 166,19</t>
+          <t>-8,85; 175,98</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>27,66; 217,85</t>
+          <t>31,81; 216,86</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>4,74; 24,11</t>
+          <t>4,41; 24,67</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,69; 18,01</t>
+          <t>-0,68; 17,47</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 8,62</t>
+          <t>-5,43; 8,68</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,7; 19,48</t>
+          <t>0,77; 19,45</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>6,06; 26,24</t>
+          <t>5,35; 25,12</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-14,95; 15,72</t>
+          <t>-18,0; 16,43</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,6; 18,98</t>
+          <t>5,78; 19,33</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>5,84; 19,65</t>
+          <t>6,17; 20,0</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-10,51; 9,72</t>
+          <t>-11,81; 10,06</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>31,67; 495,48</t>
+          <t>25,58; 563,64</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 364,98</t>
+          <t>-10,0; 416,22</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-54,95; 194,18</t>
+          <t>-45,4; 196,32</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1,35; 234,05</t>
+          <t>0,69; 228,99</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>27,41; 312,68</t>
+          <t>24,89; 310,55</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-79,68; 136,65</t>
+          <t>-84,86; 149,27</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>43,87; 240,96</t>
+          <t>42,64; 268,69</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>38,6; 246,99</t>
+          <t>42,25; 264,55</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-74,18; 99,55</t>
+          <t>-74,84; 109,81</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-15,06; 3,92</t>
+          <t>-14,09; 4,08</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-12,29; 5,12</t>
+          <t>-13,06; 4,78</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-16,67; -1,33</t>
+          <t>-17,0; -1,21</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-11,74; 6,57</t>
+          <t>-12,41; 5,9</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-12,96; 6,37</t>
+          <t>-12,98; 5,89</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-6,93; 9,38</t>
+          <t>-7,16; 9,25</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-10,65; 3,47</t>
+          <t>-10,91; 3,48</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-10,2; 3,09</t>
+          <t>-10,68; 2,41</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-8,84; 2,78</t>
+          <t>-9,35; 2,3</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-72,67; 33,67</t>
+          <t>-69,62; 35,97</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-57,73; 45,6</t>
+          <t>-60,62; 44,47</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-73,86; -8,87</t>
+          <t>-73,57; -4,35</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-46,29; 40,39</t>
+          <t>-48,55; 38,65</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-52,47; 43,52</t>
+          <t>-53,18; 44,16</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-25,62; 65,65</t>
+          <t>-27,98; 64,57</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-47,66; 21,9</t>
+          <t>-47,49; 24,35</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-46,74; 19,63</t>
+          <t>-48,24; 16,58</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-39,0; 19,32</t>
+          <t>-39,61; 15,85</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>3,19; 12,95</t>
+          <t>3,45; 12,68</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 6,0</t>
+          <t>-1,86; 6,21</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0,04; 7,1</t>
+          <t>0,04; 7,14</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2,9; 12,11</t>
+          <t>3,29; 12,2</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>0,49; 9,18</t>
+          <t>0,18; 9,47</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-8,48; 11,13</t>
+          <t>-6,6; 11,08</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>4,23; 10,88</t>
+          <t>4,51; 11,03</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0,43; 6,9</t>
+          <t>0,73; 7,07</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 8,02</t>
+          <t>-3,15; 7,88</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>20,96; 117,76</t>
+          <t>22,5; 117,73</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-12,4; 56,32</t>
+          <t>-12,48; 60,9</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 65,22</t>
+          <t>-0,84; 67,21</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>13,02; 73,01</t>
+          <t>15,41; 74,93</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>2,49; 55,22</t>
+          <t>0,65; 59,64</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-36,13; 63,4</t>
+          <t>-34,78; 62,42</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>23,17; 72,97</t>
+          <t>25,45; 76,46</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>2,21; 46,54</t>
+          <t>3,94; 46,12</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-17,69; 52,2</t>
+          <t>-16,75; 51,68</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/LAWTONB_2R3-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/LAWTONB_2R3-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13,54</t>
+          <t>12,6</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,85</t>
+          <t>21,91</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>17,97</t>
+          <t>17,4</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 26,34</t>
+          <t>-7,91; 26,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,09; 23,46</t>
+          <t>-9,76; 22,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 28,25</t>
+          <t>-3,23; 26,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,83; 46,49</t>
+          <t>9,41; 48,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,94; 40,25</t>
+          <t>0,66; 41,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,41; 35,18</t>
+          <t>4,99; 35,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,51; 31,93</t>
+          <t>6,31; 32,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,94; 29,81</t>
+          <t>1,63; 26,59</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,95; 28,0</t>
+          <t>7,22; 27,89</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>124,04%</t>
+          <t>124,41%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>109,56%</t>
+          <t>106,04%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-41,92; 335,94</t>
+          <t>-36,11; 366,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-46,14; 345,17</t>
+          <t>-44,47; 387,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-15,15; 474,07</t>
+          <t>-19,48; 390,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25,41; 559,61</t>
+          <t>24,66; 666,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 552,6</t>
+          <t>-6,75; 549,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,42; 447,73</t>
+          <t>12,75; 452,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,71; 304,08</t>
+          <t>25,42; 302,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,48; 290,72</t>
+          <t>4,48; 252,63</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21,28; 291,0</t>
+          <t>27,19; 297,23</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,61</t>
+          <t>0,37</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,98</t>
+          <t>19,57</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>11,99</t>
+          <t>12,04</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 23,15</t>
+          <t>-3,65; 23,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,93; 7,86</t>
+          <t>-12,23; 7,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,51; 10,36</t>
+          <t>-10,98; 10,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,75; 29,63</t>
+          <t>6,18; 30,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,85; 23,98</t>
+          <t>-0,08; 23,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,82; 27,72</t>
+          <t>10,86; 28,59</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,96; 23,61</t>
+          <t>5,58; 22,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 14,03</t>
+          <t>-2,47; 13,95</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,18; 18,49</t>
+          <t>4,11; 19,0</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>139,6%</t>
+          <t>143,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,72%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-35,33; 394,57</t>
+          <t>-29,54; 465,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-70,17; 179,2</t>
+          <t>-70,1; 177,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-60,16; 207,66</t>
+          <t>-61,93; 201,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33,68; 353,53</t>
+          <t>24,71; 354,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 261,99</t>
+          <t>-3,79; 271,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,99; 319,71</t>
+          <t>50,5; 327,66</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,44; 260,43</t>
+          <t>32,59; 253,69</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-14,74; 159,14</t>
+          <t>-16,98; 153,53</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,45; 204,85</t>
+          <t>23,29; 228,6</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14,76</t>
+          <t>14,54</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,19</t>
+          <t>12,93</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>12,52</t>
+          <t>12,82</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,05; 28,88</t>
+          <t>1,57; 30,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,01; 14,27</t>
+          <t>-7,57; 13,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,44; 24,85</t>
+          <t>3,32; 24,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,34; 16,52</t>
+          <t>-9,55; 17,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-21,73; 3,67</t>
+          <t>-20,45; 2,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,24; 23,58</t>
+          <t>0,21; 23,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 19,09</t>
+          <t>-2,18; 17,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-12,99; 4,66</t>
+          <t>-13,32; 3,96</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,49; 21,27</t>
+          <t>3,84; 20,8</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>155,13%</t>
+          <t>152,83%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>64,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>79,57%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 767,28</t>
+          <t>-9,2; 678,44</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-58,21; 375,66</t>
+          <t>-52,59; 314,38</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,81; 611,39</t>
+          <t>8,07; 588,47</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-36,36; 113,66</t>
+          <t>-37,5; 124,6</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-80,4; 38,61</t>
+          <t>-78,18; 24,38</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 172,88</t>
+          <t>-0,66; 176,83</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-10,74; 163,87</t>
+          <t>-11,45; 160,03</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-61,68; 43,43</t>
+          <t>-59,86; 38,07</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18,86; 203,83</t>
+          <t>14,16; 191,94</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12,29</t>
+          <t>11,65</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-1,36</t>
+          <t>-1,56</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4,5</t>
+          <t>4,07</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,6; 32,81</t>
+          <t>7,0; 32,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,98; 23,55</t>
+          <t>2,46; 23,51</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,87; 21,65</t>
+          <t>1,36; 19,72</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-10,63; 15,87</t>
+          <t>-9,35; 17,95</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-19,47; 10,66</t>
+          <t>-18,05; 8,93</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-12,56; 9,25</t>
+          <t>-13,7; 8,13</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 19,68</t>
+          <t>0,62; 20,68</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 12,25</t>
+          <t>-7,47; 12,2</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 11,97</t>
+          <t>-3,59; 11,44</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>193,98%</t>
+          <t>183,94%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-5,68%</t>
+          <t>-6,51%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>24,77%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>42,96; 1592,3</t>
+          <t>46,04; 1526,83</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,02; 1113,27</t>
+          <t>0,22; 982,21</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,11; 932,89</t>
+          <t>-7,68; 970,8</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-37,35; 94,74</t>
+          <t>-30,86; 111,92</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-59,28; 69,2</t>
+          <t>-60,38; 60,88</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-37,89; 55,49</t>
+          <t>-41,74; 47,83</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 169,42</t>
+          <t>-0,28; 181,13</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-27,43; 104,15</t>
+          <t>-34,28; 101,54</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-15,73; 104,84</t>
+          <t>-17,36; 103,4</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-4,93</t>
+          <t>-5,45</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-6,27</t>
+          <t>-6,24</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-5,59</t>
+          <t>-5,77</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-25,77; 16,13</t>
+          <t>-24,98; 17,97</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-35,94; -1,49</t>
+          <t>-33,61; 0,14</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-24,27; 10,76</t>
+          <t>-24,64; 10,06</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-20,94; 17,33</t>
+          <t>-21,25; 16,49</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-13,22; 26,02</t>
+          <t>-14,33; 26,22</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-23,22; 8,35</t>
+          <t>-24,2; 9,27</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-17,9; 11,08</t>
+          <t>-16,95; 11,58</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-18,2; 10,22</t>
+          <t>-18,39; 8,95</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-17,93; 6,0</t>
+          <t>-18,0; 6,66</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-18,63%</t>
+          <t>-20,58%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-20,47%</t>
+          <t>-20,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-19,34%</t>
+          <t>-19,97%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-72,93; 110,12</t>
+          <t>-72,97; 124,08</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-91,71; 6,92</t>
+          <t>-89,41; 14,7</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-63,75; 83,34</t>
+          <t>-61,56; 66,69</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-52,73; 91,88</t>
+          <t>-53,09; 84,29</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-33,52; 131,63</t>
+          <t>-36,24; 133,77</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-52,88; 45,3</t>
+          <t>-55,16; 50,88</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-49,22; 54,99</t>
+          <t>-46,74; 56,42</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-51,1; 49,5</t>
+          <t>-50,47; 44,08</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-46,5; 29,7</t>
+          <t>-47,07; 38,04</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>13,12</t>
+          <t>13,27</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,81</t>
+          <t>20,15</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>17,2</t>
+          <t>16,97</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 29,1</t>
+          <t>-7,14; 27,04</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-9,27; 21,62</t>
+          <t>-10,66; 20,65</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,26; 26,32</t>
+          <t>-0,62; 25,78</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 24,46</t>
+          <t>-3,33; 25,11</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 28,72</t>
+          <t>-3,01; 29,0</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,42; 31,62</t>
+          <t>6,38; 30,89</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,14; 21,29</t>
+          <t>1,0; 20,37</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 21,59</t>
+          <t>-1,55; 21,44</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>7,87; 25,26</t>
+          <t>7,59; 25,21</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>124,66%</t>
+          <t>120,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>99,89%</t>
+          <t>98,57%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-25,4; 266,81</t>
+          <t>-32,8; 245,46</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-38,98; 206,78</t>
+          <t>-42,14; 203,66</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 295,06</t>
+          <t>-3,83; 269,4</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-21,91; 230,41</t>
+          <t>-15,42; 264,21</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-16,65; 278,97</t>
+          <t>-15,41; 290,73</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>28,38; 371,27</t>
+          <t>21,68; 304,02</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0,21; 186,33</t>
+          <t>4,72; 167,93</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-8,85; 175,98</t>
+          <t>-9,26; 170,65</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>31,81; 216,86</t>
+          <t>31,22; 222,11</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1,59</t>
+          <t>1,46</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-2,24</t>
+          <t>14,15</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-0,26</t>
+          <t>8,03</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>4,41; 24,67</t>
+          <t>4,65; 24,58</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 17,47</t>
+          <t>0,55; 17,93</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 8,68</t>
+          <t>-6,21; 7,86</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,77; 19,45</t>
+          <t>0,77; 19,96</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>5,35; 25,12</t>
+          <t>5,1; 24,79</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-18,0; 16,43</t>
+          <t>5,8; 22,41</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,78; 19,33</t>
+          <t>5,46; 19,03</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>6,17; 20,0</t>
+          <t>6,22; 19,41</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-11,81; 10,06</t>
+          <t>2,25; 13,6</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-17,46%</t>
+          <t>110,34%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-2,46%</t>
+          <t>75,47%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>25,58; 563,64</t>
+          <t>26,06; 496,27</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-10,0; 416,22</t>
+          <t>0,79; 406,79</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-45,4; 196,32</t>
+          <t>-50,55; 174,55</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>0,69; 228,99</t>
+          <t>-1,35; 224,43</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>24,89; 310,55</t>
+          <t>25,57; 310,34</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-84,86; 149,27</t>
+          <t>25,44; 265,07</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>42,64; 268,69</t>
+          <t>40,69; 234,9</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>42,25; 264,55</t>
+          <t>43,38; 246,32</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-74,84; 109,81</t>
+          <t>13,5; 170,15</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-8,6</t>
+          <t>-8,21</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,66</t>
+          <t>2,3</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-2,9</t>
+          <t>-2,28</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-14,09; 4,08</t>
+          <t>-13,72; 4,49</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-13,06; 4,78</t>
+          <t>-13,28; 4,68</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-17,0; -1,21</t>
+          <t>-16,0; -1,0</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-12,41; 5,9</t>
+          <t>-11,86; 7,4</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-12,98; 5,89</t>
+          <t>-13,32; 4,5</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-7,16; 9,25</t>
+          <t>-6,22; 10,7</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-10,91; 3,48</t>
+          <t>-10,59; 2,76</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-10,68; 2,41</t>
+          <t>-10,63; 2,31</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-9,35; 2,3</t>
+          <t>-8,3; 3,32</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-52,36%</t>
+          <t>-49,94%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-15,35%</t>
+          <t>-12,06%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-69,62; 35,97</t>
+          <t>-68,22; 43,24</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-60,62; 44,47</t>
+          <t>-60,53; 42,27</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-73,57; -4,35</t>
+          <t>-72,27; -1,93</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-48,55; 38,65</t>
+          <t>-46,03; 51,43</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-53,18; 44,16</t>
+          <t>-52,43; 29,19</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-27,98; 64,57</t>
+          <t>-23,35; 74,41</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-47,49; 24,35</t>
+          <t>-47,24; 18,54</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-48,24; 16,58</t>
+          <t>-48,99; 16,3</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-39,61; 15,85</t>
+          <t>-35,65; 23,75</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>3,68</t>
+          <t>3,12</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>4,15</t>
+          <t>9,84</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>4,2</t>
+          <t>6,78</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>3,45; 12,68</t>
+          <t>3,25; 12,5</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 6,21</t>
+          <t>-1,55; 6,3</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0,04; 7,14</t>
+          <t>-0,65; 6,82</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3,29; 12,2</t>
+          <t>3,03; 12,18</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>0,18; 9,47</t>
+          <t>0,17; 9,45</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 11,08</t>
+          <t>6,31; 13,59</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>4,51; 11,03</t>
+          <t>4,38; 10,75</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0,73; 7,07</t>
+          <t>0,65; 6,71</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 7,88</t>
+          <t>4,03; 9,77</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>52,92%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>41,99%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>22,5; 117,73</t>
+          <t>20,35; 112,15</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-12,48; 60,9</t>
+          <t>-10,7; 60,18</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 67,21</t>
+          <t>-3,98; 65,44</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>15,41; 74,93</t>
+          <t>14,16; 75,4</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>0,65; 59,64</t>
+          <t>0,17; 56,97</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-34,78; 62,42</t>
+          <t>30,66; 87,2</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>25,45; 76,46</t>
+          <t>24,38; 72,9</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>3,94; 46,12</t>
+          <t>3,36; 45,12</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-16,75; 51,68</t>
+          <t>22,35; 69,0</t>
         </is>
       </c>
     </row>
